--- a/artfynd/A 44828-2025 artfynd.xlsx
+++ b/artfynd/A 44828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339781</v>
       </c>
       <c r="B2" t="n">
-        <v>91374</v>
+        <v>91386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44828-2025 artfynd.xlsx
+++ b/artfynd/A 44828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339781</v>
       </c>
       <c r="B2" t="n">
-        <v>91386</v>
+        <v>91388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44828-2025 artfynd.xlsx
+++ b/artfynd/A 44828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339781</v>
       </c>
       <c r="B2" t="n">
-        <v>91388</v>
+        <v>91389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44828-2025 artfynd.xlsx
+++ b/artfynd/A 44828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339781</v>
       </c>
       <c r="B2" t="n">
-        <v>91389</v>
+        <v>91416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44828-2025 artfynd.xlsx
+++ b/artfynd/A 44828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339781</v>
       </c>
       <c r="B2" t="n">
-        <v>91416</v>
+        <v>91426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44828-2025 artfynd.xlsx
+++ b/artfynd/A 44828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339781</v>
       </c>
       <c r="B2" t="n">
-        <v>91426</v>
+        <v>91430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44828-2025 artfynd.xlsx
+++ b/artfynd/A 44828-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128339781</v>
       </c>
       <c r="B2" t="n">
-        <v>91430</v>
+        <v>91831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
